--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>1</v>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>1</v>
@@ -9416,7 +9416,7 @@
         <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -12811,7 +12811,7 @@
         <v>3</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$193</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 91 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 87 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA192"/>
+  <dimension ref="A1:AA193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X38" s="9" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6126,8 +6126,8 @@
       <c r="S56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7890,8 +7890,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
@@ -12049,11 +12049,11 @@
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>0</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>4</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12422,8 +12422,8 @@
       <c r="P121" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13301,8 +13301,8 @@
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="9" t="n">
-        <v>1</v>
+      <c r="S130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T130" s="10" t="n">
         <v>1</v>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -13698,11 +13698,11 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" s="9" t="n">
-        <v>0</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W134" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X134" s="10" t="n">
         <v>5</v>
@@ -13710,8 +13710,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -16356,7 +16356,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="9" t="n">
         <v>0</v>
@@ -16408,8 +16408,8 @@
       <c r="S162" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T162" s="9" t="n">
-        <v>0</v>
+      <c r="T162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U162" s="9" t="n">
         <v>0</v>
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -17382,7 +17382,7 @@
         <v>1</v>
       </c>
       <c r="U172" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V172" s="10" t="n">
         <v>4</v>
@@ -17467,7 +17467,7 @@
         <v>2</v>
       </c>
       <c r="Q173" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>0</v>
@@ -19161,15 +19161,15 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>6642875</v>
+        <v>28680923</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+          <t>Raisoni Institutes Amethyst Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -19183,13 +19183,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
@@ -19227,14 +19227,14 @@
       <c r="U191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V191" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W191" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="X191" s="10" t="n">
-        <v>4</v>
+      <c r="V191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X191" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -19258,93 +19258,190 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
+        <v>6642875</v>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F192" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G192" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J192" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K192" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L192" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M192" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O192" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W192" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X192" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA192" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="n">
         <v>28678983</v>
       </c>
-      <c r="D192" s="4" t="inlineStr">
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>Ultratech Rise Toastmasters Club</t>
         </is>
       </c>
-      <c r="E192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G192" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H192" s="4" t="inlineStr">
+      <c r="E193" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="8" t="inlineStr">
+      <c r="I193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M192" s="7" t="n">
+      <c r="M193" s="7" t="n">
         <v>46387</v>
       </c>
-      <c r="N192" s="4" t="inlineStr">
+      <c r="N193" s="4" t="inlineStr">
         <is>
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O192" s="8" t="inlineStr">
+      <c r="O193" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z192" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA192" s="9" t="n">
+      <c r="P193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA192"/>
+  <autoFilter ref="A1:AA193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19761,7 +19858,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -19893,7 +19990,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -20190,7 +20287,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -20205,7 +20302,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -20223,7 +20320,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -20289,7 +20386,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -20322,7 +20419,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20520,7 +20617,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -20715,16 +20812,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -20733,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$194</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 87 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 68 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA193"/>
+  <dimension ref="A1:AA194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,8 +1876,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2440,8 +2440,8 @@
       <c r="S18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>1</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" s="9" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L36" s="8" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="9" t="n">
         <v>0</v>
@@ -4192,8 +4192,8 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>3</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>1</v>
@@ -4689,8 +4689,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>84</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="P45" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>1</v>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5633,13 +5633,13 @@
         <v>4</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="9" t="n">
-        <v>1</v>
+      <c r="S51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T51" s="10" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6114,8 +6114,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P56" s="9" t="n">
-        <v>3</v>
+      <c r="P56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="P57" s="10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q57" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R57" s="9" t="n">
-        <v>0</v>
+      <c r="R57" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S57" s="9" t="n">
         <v>0</v>
@@ -7400,7 +7400,7 @@
         <v>1</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -8078,8 +8078,8 @@
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X76" s="9" t="n">
-        <v>3</v>
+      <c r="X76" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8854,8 +8854,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>2</v>
+      <c r="X84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>1</v>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10218,8 +10218,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
@@ -11167,14 +11167,14 @@
       <c r="R108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>1</v>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T108" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
+      <c r="U108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V108" s="9" t="n">
         <v>0</v>
@@ -11188,8 +11188,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11549,8 +11549,8 @@
       <c r="P112" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" s="9" t="n">
-        <v>1</v>
+      <c r="Q112" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11653,7 +11653,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12177,11 +12177,11 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28677039</v>
+        <v>28680780</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>CDK Global Toastmasters</t>
+          <t>Bloomberg Pune Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>0</v>
@@ -12249,8 +12249,8 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="10" t="n">
-        <v>6</v>
+      <c r="X119" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>5163301</v>
+        <v>28677039</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Deccan Toastmasters Club</t>
+          <t>CDK Global Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12322,32 +12322,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P120" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q120" s="10" t="n">
-        <v>2</v>
+      <c r="P120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28676239</v>
+        <v>5163301</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Icertis Toastmasters Club</t>
+          <t>Deccan Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12419,8 +12419,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P121" s="9" t="n">
-        <v>3</v>
+      <c r="P121" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q121" s="10" t="n">
         <v>2</v>
@@ -12435,16 +12435,16 @@
         <v>1</v>
       </c>
       <c r="U121" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -12468,15 +12468,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28677867</v>
+        <v>28676239</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Pune Salesforce Toastmasters Club</t>
+          <t>Icertis Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,25 +12490,25 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L122" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
@@ -12516,23 +12516,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" s="9" t="n">
-        <v>0</v>
+      <c r="P122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q122" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
         <v>0</v>
@@ -12540,17 +12540,17 @@
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="9" t="n">
-        <v>0</v>
+      <c r="X122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA122" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>2541278</v>
+        <v>28677867</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club Of Pune-Central</t>
+          <t>Pune Salesforce Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -12601,11 +12601,11 @@
         </is>
       </c>
       <c r="M123" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O123" s="8" t="inlineStr">
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -12632,13 +12632,13 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="10" t="n">
-        <v>4</v>
+      <c r="X123" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -12646,8 +12646,8 @@
       <c r="Z123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA123" s="10" t="n">
-        <v>1</v>
+      <c r="AA123" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -12658,15 +12658,15 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28679940</v>
+        <v>2541278</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>ACA Global Toastmasters Club</t>
+          <t>Toastmasters Club Of Pune-Central</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -12711,10 +12711,10 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
@@ -12729,13 +12729,13 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X124" s="9" t="n">
-        <v>0</v>
+      <c r="X124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28678482</v>
+        <v>28679940</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Emerson Eloquence Toastmasters Club</t>
+          <t>ACA Global Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,10 +12781,10 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K125" s="4" t="n">
         <v>0</v>
@@ -12808,16 +12808,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -12831,14 +12831,14 @@
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X125" s="10" t="n">
-        <v>7</v>
+      <c r="X125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7856700</v>
+        <v>28678482</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Evolent India Toastmasters Club</t>
+          <t>Emerson Eloquence Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>1</v>
@@ -12914,13 +12914,13 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T126" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
         <v>0</v>
@@ -12928,14 +12928,14 @@
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>1</v>
+      <c r="X126" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -12953,15 +12953,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28678042</v>
+        <v>7856700</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Sodales India Toastmasters Club</t>
+          <t>Evolent India Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,10 +12975,10 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>0</v>
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13013,11 +13013,11 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V127" s="9" t="n">
         <v>0</v>
@@ -13025,8 +13025,8 @@
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="10" t="n">
-        <v>4</v>
+      <c r="X127" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1534609</v>
+        <v>28678042</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune-West</t>
+          <t>Sodales India Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,17 +13072,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q128" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13116,20 +13116,20 @@
       <c r="U128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="10" t="n">
+      <c r="V128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W128" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X128" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="10" t="n">
-        <v>1</v>
+      <c r="Z128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13138,24 +13138,24 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>2571105</v>
+        <v>1534609</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Opulent Toastmasters Club Of Pune Camp</t>
+          <t>Toastmasters Club of Pune-West</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
@@ -13196,37 +13196,37 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U129" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>5294613</v>
+        <v>2571105</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Pune Advanced Toastmasters Club</t>
+          <t>Opulent Toastmasters Club Of Pune Camp</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13301,29 +13301,29 @@
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="10" t="n">
+      <c r="S130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" s="10" t="n">
+      <c r="V130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W130" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="10" t="n">
-        <v>1</v>
+      <c r="Z130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7985954</v>
+        <v>5294613</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Ace Toastmasters Club</t>
+          <t>Pune Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13389,8 +13389,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P131" s="10" t="n">
-        <v>6</v>
+      <c r="P131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -13398,20 +13398,20 @@
       <c r="R131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S131" s="9" t="n">
-        <v>0</v>
+      <c r="S131" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
+      <c r="U131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W131" s="10" t="n">
-        <v>9</v>
+      <c r="W131" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -13438,15 +13438,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28678890</v>
+        <v>7985954</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Rocket Sofware Pune</t>
+          <t>Raisoni Ace Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -13486,8 +13486,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P132" s="9" t="n">
-        <v>0</v>
+      <c r="P132" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -13498,26 +13498,26 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" s="9" t="n">
-        <v>0</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W132" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,11 +13535,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28679159</v>
+        <v>28678890</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Pune</t>
+          <t>Toastmasters Club of Rocket Sofware Pune</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -13557,25 +13557,25 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K133" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O133" s="8" t="inlineStr">
@@ -13607,8 +13607,8 @@
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="9" t="n">
-        <v>0</v>
+      <c r="X133" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -13616,8 +13616,8 @@
       <c r="Z133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA133" s="9" t="n">
-        <v>0</v>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -13628,19 +13628,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28679554</v>
+        <v>28679159</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>CGI Pune Toastmasters Club</t>
+          <t>UKG Toastmasters Pune</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,25 +13654,25 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
@@ -13698,23 +13698,23 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W134" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X134" s="10" t="n">
-        <v>5</v>
+      <c r="V134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
+      <c r="Z134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28676666</v>
+        <v>28679554</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Dr D Y Patil Community Toastmaster Club</t>
+          <t>CGI Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="7" t="n">
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13789,26 +13789,26 @@
       <c r="S135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U135" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W135" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28679580</v>
+        <v>28676666</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Teaching Titans Toastmasters Club</t>
+          <t>Dr D Y Patil Community Toastmaster Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L136" s="8" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -13886,11 +13886,11 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V136" s="9" t="n">
         <v>0</v>
@@ -13898,8 +13898,8 @@
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>0</v>
+      <c r="X136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>6097544</v>
+        <v>28679580</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters for Pune Entrepreneurs</t>
+          <t>Teaching Titans Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -13972,16 +13972,16 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S137" s="10" t="n">
-        <v>2</v>
+      <c r="S137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -13990,19 +13990,19 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="10" t="n">
-        <v>7</v>
+      <c r="X137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14016,19 +14016,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28678211</v>
+        <v>6097544</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Burckhardt Compression Toastmasters Club 1.0</t>
+          <t>Toastmasters for Pune Entrepreneurs</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,25 +14042,25 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O138" s="8" t="inlineStr">
@@ -14069,16 +14069,16 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="9" t="n">
-        <v>0</v>
+      <c r="S138" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T138" s="9" t="n">
         <v>0</v>
@@ -14087,22 +14087,22 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+      <c r="X138" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28676267</v>
+        <v>28678211</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>GCD Toastmasters Club</t>
+          <t>Burckhardt Compression Toastmasters Club 1.0</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14153,11 +14153,11 @@
         </is>
       </c>
       <c r="M139" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O139" s="8" t="inlineStr">
@@ -14189,17 +14189,17 @@
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="10" t="n">
-        <v>4</v>
+      <c r="X139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28676682</v>
+        <v>28676267</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Pattern India Toastmasters Club</t>
+          <t>GCD Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="7" t="n">
@@ -14292,8 +14292,8 @@
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>7448369</v>
+        <v>28676682</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters for Pune Entrepreneurs 2.0</t>
+          <t>Pattern India Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -14369,22 +14369,22 @@
         <v>0</v>
       </c>
       <c r="S141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T141" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="10" t="n">
+      <c r="V141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X141" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X141" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14404,19 +14404,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>6592020</v>
+        <v>7448369</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Pune Toastmasters Club</t>
+          <t>Toastmasters for Pune Entrepreneurs 2.0</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -14456,8 +14456,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P142" s="9" t="n">
-        <v>0</v>
+      <c r="P142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14466,28 +14466,28 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="9" t="n">
-        <v>1</v>
+      <c r="V142" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>7870960</v>
+        <v>6592020</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Mastering Leadership TMC</t>
+          <t>Deutsche Bank Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="7" t="n">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -14572,19 +14572,19 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="10" t="n">
-        <v>1</v>
+      <c r="Z143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28677938</v>
+        <v>7870960</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Blaze Toastmasters Club</t>
+          <t>Mastering Leadership TMC</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14668,11 +14668,11 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W144" s="10" t="n">
-        <v>5</v>
+      <c r="V144" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
         <v>7</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>7757012</v>
+        <v>28677938</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of BMC Software Customer Success</t>
+          <t>Raisoni Blaze Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,17 +14721,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J145" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J145" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="7" t="n">
@@ -14765,11 +14765,11 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W145" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X145" s="10" t="n">
         <v>7</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -14792,19 +14792,19 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28675867</v>
+        <v>7757012</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Avalara Pune Toastmasters Club</t>
+          <t>Toastmasters Club of BMC Software Customer Success</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -14832,11 +14832,11 @@
         </is>
       </c>
       <c r="M146" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O146" s="8" t="inlineStr">
@@ -14863,22 +14863,22 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X146" s="9" t="n">
-        <v>0</v>
+      <c r="X146" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>3700901</v>
+        <v>28675867</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of BMC Software</t>
+          <t>Avalara Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
@@ -14929,11 +14929,11 @@
         </is>
       </c>
       <c r="M147" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O147" s="8" t="inlineStr">
@@ -14945,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -14960,22 +14960,22 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="10" t="n">
-        <v>7</v>
+      <c r="X147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA147" s="10" t="n">
-        <v>1</v>
+      <c r="Z147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -14990,15 +14990,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1141787</v>
+        <v>3700901</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune</t>
+          <t>Toastmasters Club of BMC Software</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -15038,29 +15038,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P148" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q148" s="10" t="n">
+      <c r="P148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T148" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U148" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="V148" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W148" s="10" t="n">
-        <v>5</v>
+      <c r="W148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X148" s="10" t="n">
         <v>7</v>
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>2973814</v>
+        <v>1141787</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune - North East</t>
+          <t>Toastmasters Club of Pune</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15135,38 +15135,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R149" s="9" t="n">
-        <v>0</v>
+      <c r="P149" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q149" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R149" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V149" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W149" s="9" t="n">
-        <v>1</v>
+      <c r="W149" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="9" t="n">
-        <v>0</v>
+      <c r="Z149" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>28678894</v>
+        <v>2973814</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Vertiv Pune Toastmasters Club</t>
+          <t>Toastmasters Club of Pune - North East</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>1</v>
@@ -15250,20 +15250,20 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>0</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X150" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -15272,24 +15272,24 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>6539289</v>
+        <v>28678894</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Cosmic Toastmasters Club</t>
+          <t>Vertiv Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15341,11 +15341,11 @@
       <c r="S151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U151" s="10" t="n">
-        <v>1</v>
+      <c r="T151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
         <v>0</v>
@@ -15353,8 +15353,8 @@
       <c r="W151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X151" s="9" t="n">
-        <v>0</v>
+      <c r="X151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15378,15 +15378,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>7709645</v>
+        <v>6539289</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>E3 Ecolab Toastmasters Club</t>
+          <t>Cosmic Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,17 +15400,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K152" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L152" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M152" s="7" t="n">
@@ -15438,11 +15438,11 @@
       <c r="S152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" s="9" t="n">
-        <v>0</v>
+      <c r="T152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V152" s="9" t="n">
         <v>0</v>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -15475,15 +15475,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>28678780</v>
+        <v>7709645</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Michelin Toastmasters Club</t>
+          <t>E3 Ecolab Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="7" t="n">
@@ -15523,38 +15523,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P153" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q153" s="10" t="n">
+      <c r="P153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R153" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V153" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W153" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X153" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="10" t="n">
-        <v>1</v>
+      <c r="Z153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -15572,15 +15572,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>7780150</v>
+        <v>28678780</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Wonders of Women Toastmasters Club</t>
+          <t>Michelin Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
@@ -15620,32 +15620,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q154" s="9" t="n">
-        <v>1</v>
+      <c r="P154" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q154" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S154" s="9" t="n">
-        <v>1</v>
+      <c r="S154" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T154" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V154" s="9" t="n">
-        <v>1</v>
+      <c r="U154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W154" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -15665,19 +15665,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>5144305</v>
+        <v>7780150</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Barclays Pune Toastmasters Club</t>
+          <t>Wonders of Women Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -15721,22 +15721,22 @@
         <v>0</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -15766,15 +15766,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>28679346</v>
+        <v>5144305</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Club 3.0</t>
+          <t>Barclays Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,10 +15788,10 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K156" s="4" t="n">
         <v>0</v>
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -15839,13 +15839,13 @@
         <v>0</v>
       </c>
       <c r="X156" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -15863,15 +15863,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>7922639</v>
+        <v>28679346</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters 3.0</t>
+          <t>Eaton Toastmasters Club 3.0</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J157" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -15923,20 +15923,20 @@
       <c r="S157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T157" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U157" s="10" t="n">
-        <v>1</v>
+      <c r="T157" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -15960,15 +15960,15 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>28679461</v>
+        <v>7922639</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Serum Pune Toastmasters Club</t>
+          <t>John Deere Pune Toastmasters 3.0</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q158" s="9" t="n">
         <v>0</v>
@@ -16020,26 +16020,26 @@
       <c r="S158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W158" s="10" t="n">
-        <v>15</v>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W158" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X158" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -16053,19 +16053,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>1813871</v>
+        <v>28679461</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>ADP Pune Toastmasters</t>
+          <t>Serum Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16108,14 +16108,14 @@
       <c r="P159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" s="10" t="n">
-        <v>2</v>
+      <c r="Q159" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T159" s="9" t="n">
         <v>0</v>
@@ -16123,11 +16123,11 @@
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W159" s="9" t="n">
-        <v>0</v>
+      <c r="V159" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W159" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16154,15 +16154,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>6006628</v>
+        <v>1813871</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Allstate Toastmasters Club Pune</t>
+          <t>ADP Pune Toastmasters</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -16203,16 +16203,16 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q160" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R160" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S160" s="10" t="n">
-        <v>2</v>
+      <c r="R160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T160" s="9" t="n">
         <v>0</v>
@@ -16221,7 +16221,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -16232,8 +16232,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="10" t="n">
-        <v>1</v>
+      <c r="Z160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16251,15 +16251,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>28677687</v>
+        <v>6006628</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Excellence Club</t>
+          <t>Allstate Toastmasters Club Pune</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16273,17 +16273,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K161" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L161" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M161" s="7" t="n">
@@ -16300,16 +16300,16 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q161" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R161" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S161" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T161" s="9" t="n">
         <v>0</v>
@@ -16329,8 +16329,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -16348,15 +16348,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>6691907</v>
+        <v>28677687</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>RISE Toastmasters Club, Magarpatta</t>
+          <t>Eaton Toastmasters Excellence Club</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16370,17 +16370,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="7" t="n">
@@ -16406,19 +16406,19 @@
         <v>0</v>
       </c>
       <c r="S162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T162" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W162" s="10" t="n">
-        <v>9</v>
+      <c r="V162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>7</v>
@@ -16426,8 +16426,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="10" t="n">
-        <v>1</v>
+      <c r="Z162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -16441,19 +16441,19 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>28678887</v>
+        <v>6691907</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Allianz Technology Toastmasters Club 2.0</t>
+          <t>RISE Toastmasters Club, Magarpatta</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -16481,11 +16481,11 @@
         </is>
       </c>
       <c r="M163" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O163" s="8" t="inlineStr">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -16503,31 +16503,31 @@
         <v>0</v>
       </c>
       <c r="S163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W163" s="9" t="n">
-        <v>0</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W163" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X163" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA163" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -16542,15 +16542,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>28680266</v>
+        <v>28678887</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Hoerbiger Pune Toastmasters Club</t>
+          <t>Allianz Technology Toastmasters Club 2.0</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16564,10 +16564,10 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K164" s="4" t="n">
         <v>0</v>
@@ -16578,11 +16578,11 @@
         </is>
       </c>
       <c r="M164" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O164" s="8" t="inlineStr">
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" s="9" t="n">
         <v>0</v>
@@ -16615,16 +16615,16 @@
         <v>0</v>
       </c>
       <c r="X164" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA164" s="10" t="n">
-        <v>1</v>
+      <c r="Z164" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -16639,15 +16639,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>2187981</v>
+        <v>28680266</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters Club</t>
+          <t>Hoerbiger Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16661,17 +16661,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L165" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M165" s="7" t="n">
@@ -16706,19 +16706,19 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X165" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -16736,11 +16736,11 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>7327561</v>
+        <v>2187981</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Teradata Pune Toastmasters Club</t>
+          <t>John Deere Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L166" s="8" t="inlineStr">
         <is>
@@ -16803,13 +16803,13 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X166" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
@@ -16833,15 +16833,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>1543586</v>
+        <v>7327561</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune South East</t>
+          <t>Teradata Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -16855,17 +16855,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="7" t="n">
@@ -16882,7 +16882,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -16893,20 +16893,20 @@
       <c r="S167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V167" s="10" t="n">
-        <v>4</v>
+      <c r="T167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
@@ -16926,19 +16926,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>6783469</v>
+        <v>1543586</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>BNY Prestige Pune Toastmasters Club</t>
+          <t>Toastmasters Club of Pune South East</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -16952,13 +16952,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
         <v>0</v>
@@ -16990,26 +16990,26 @@
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" s="9" t="n">
-        <v>0</v>
+      <c r="T168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W168" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X168" s="9" t="n">
         <v>3</v>
       </c>
+      <c r="X168" s="10" t="n">
+        <v>6</v>
+      </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -17027,15 +17027,15 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>28676238</v>
+        <v>6783469</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Danfoss Toastmasters Club, Pune</t>
+          <t>BNY Prestige Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         </is>
       </c>
       <c r="P169" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q169" s="9" t="n">
         <v>0</v>
@@ -17094,19 +17094,19 @@
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X169" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X169" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="10" t="n">
-        <v>1</v>
+      <c r="Z169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
@@ -17124,15 +17124,15 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>28680588</v>
+        <v>28676238</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Eaton TMC 2.0</t>
+          <t>Danfoss Toastmasters Club, Pune</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17146,13 +17146,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" s="9" t="n">
         <v>0</v>
@@ -17191,19 +17191,19 @@
         <v>0</v>
       </c>
       <c r="V170" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W170" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X170" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z170" s="9" t="n">
-        <v>0</v>
+      <c r="Z170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA170" s="10" t="n">
         <v>1</v>
@@ -17221,15 +17221,15 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1114159</v>
+        <v>28680588</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Club</t>
+          <t>Eaton TMC 2.0</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -17272,8 +17272,8 @@
       <c r="P171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" s="10" t="n">
-        <v>2</v>
+      <c r="Q171" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -17294,7 +17294,7 @@
         <v>0</v>
       </c>
       <c r="X171" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
@@ -17318,15 +17318,15 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>7850568</v>
+        <v>1114159</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters 2.0</t>
+          <t>Eaton Toastmasters Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
@@ -17369,23 +17369,23 @@
       <c r="P172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" s="9" t="n">
-        <v>1</v>
+      <c r="Q172" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S172" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T172" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U172" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V172" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -17406,24 +17406,24 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>5297378</v>
+        <v>7850568</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Barclays Pune 2 Toastmasters</t>
+          <t>John Deere Pune Toastmasters 2.0</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
@@ -17464,31 +17464,31 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U173" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q173" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V173" s="9" t="n">
-        <v>0</v>
+      <c r="V173" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X173" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
@@ -17512,15 +17512,15 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>28676691</v>
+        <v>5297378</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>BNY Mic Master's Club</t>
+          <t>Barclays Pune 2 Toastmasters</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17534,10 +17534,10 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K174" s="4" t="n">
         <v>0</v>
@@ -17561,16 +17561,16 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q174" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q174" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R174" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S174" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T174" s="9" t="n">
         <v>0</v>
@@ -17585,13 +17585,13 @@
         <v>0</v>
       </c>
       <c r="X174" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -17609,15 +17609,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28677096</v>
+        <v>28676691</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>EEEC Pune Toastmasters Club</t>
+          <t>BNY Mic Master's Club</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17631,10 +17631,10 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K175" s="4" t="n">
         <v>0</v>
@@ -17657,32 +17657,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P175" s="10" t="n">
+      <c r="P175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X175" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="Q175" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W175" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X175" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
@@ -17706,11 +17706,11 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>7289566</v>
+        <v>28677096</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Expedition Toastmasters Pune</t>
+          <t>EEEC Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
@@ -17754,17 +17754,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q176" s="9" t="n">
-        <v>0</v>
+      <c r="P176" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q176" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S176" s="10" t="n">
-        <v>2</v>
+      <c r="S176" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T176" s="9" t="n">
         <v>0</v>
@@ -17772,8 +17772,8 @@
       <c r="U176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="10" t="n">
-        <v>4</v>
+      <c r="V176" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
@@ -17803,15 +17803,15 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>7300474</v>
+        <v>7289566</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Kharadi Toastmasters Club</t>
+          <t>Expedition Toastmasters Pune</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -17855,13 +17855,13 @@
         <v>0</v>
       </c>
       <c r="Q177" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S177" s="9" t="n">
-        <v>0</v>
+      <c r="S177" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T177" s="9" t="n">
         <v>0</v>
@@ -17873,10 +17873,10 @@
         <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -17896,19 +17896,19 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>6716037</v>
+        <v>7300474</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Aurangabad Toastmasters</t>
+          <t>Kharadi Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -17922,17 +17922,17 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L178" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M178" s="7" t="n">
@@ -17952,7 +17952,7 @@
         <v>0</v>
       </c>
       <c r="Q178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R178" s="9" t="n">
         <v>0</v>
@@ -17966,11 +17966,11 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>2</v>
+      <c r="V178" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W178" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X178" s="10" t="n">
         <v>6</v>
@@ -17978,8 +17978,8 @@
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="9" t="n">
-        <v>0</v>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
@@ -17997,11 +17997,11 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>28680879</v>
+        <v>6716037</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Everseen Toastmasters Club</t>
+          <t>Aurangabad Toastmasters</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
@@ -18019,17 +18019,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="7" t="n">
@@ -18064,7 +18064,7 @@
         <v>0</v>
       </c>
       <c r="V179" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W179" s="9" t="n">
         <v>0</v>
@@ -18076,7 +18076,7 @@
         <v>0</v>
       </c>
       <c r="Z179" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -18094,11 +18094,11 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>6941712</v>
+        <v>28680879</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Nashik</t>
+          <t>Everseen Toastmasters Club</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -18116,13 +18116,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
@@ -18160,20 +18160,20 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="10" t="n">
-        <v>4</v>
+      <c r="V180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X180" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y180" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="X180" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y180" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z180" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AA180" s="10" t="n">
         <v>1</v>
@@ -18191,15 +18191,15 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>28677802</v>
+        <v>6941712</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Voice of E76</t>
+          <t>Toastmasters Club of Nashik</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -18213,17 +18213,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M181" s="7" t="n">
@@ -18257,11 +18257,11 @@
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="9" t="n">
-        <v>0</v>
+      <c r="V181" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W181" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>4</v>
@@ -18288,15 +18288,15 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>28675765</v>
+        <v>28677802</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Wagholi Toastmasters Club</t>
+          <t>Voice of E76</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -18310,10 +18310,10 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K182" s="4" t="n">
         <v>0</v>
@@ -18361,13 +18361,13 @@
         <v>0</v>
       </c>
       <c r="X182" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z182" s="10" t="n">
-        <v>1</v>
+      <c r="Z182" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA182" s="10" t="n">
         <v>1</v>
@@ -18381,19 +18381,19 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>5757009</v>
+        <v>28675765</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>IIM Nagpur Toastmasters Club</t>
+          <t>Wagholi Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -18407,10 +18407,10 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K183" s="4" t="n">
         <v>0</v>
@@ -18457,14 +18457,14 @@
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X183" s="9" t="n">
-        <v>0</v>
+      <c r="X183" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z183" s="9" t="n">
-        <v>0</v>
+      <c r="Z183" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA183" s="10" t="n">
         <v>1</v>
@@ -18482,15 +18482,15 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>3531688</v>
+        <v>5757009</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Nagpur Toastmasters Club</t>
+          <t>IIM Nagpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -18504,17 +18504,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L184" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M184" s="7" t="n">
@@ -18531,7 +18531,7 @@
         </is>
       </c>
       <c r="P184" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q184" s="9" t="n">
         <v>0</v>
@@ -18540,28 +18540,28 @@
         <v>0</v>
       </c>
       <c r="S184" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T184" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="10" t="n">
-        <v>4</v>
+      <c r="V184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X184" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="X184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="10" t="n">
-        <v>1</v>
+      <c r="Z184" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA184" s="10" t="n">
         <v>1</v>
@@ -18579,15 +18579,15 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>7289583</v>
+        <v>3531688</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Brio Toastmasters Club</t>
+          <t>Nagpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -18601,13 +18601,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
@@ -18628,31 +18628,31 @@
         </is>
       </c>
       <c r="P185" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U185" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W185" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S185" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U185" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V185" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W185" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X185" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y185" s="9" t="n">
         <v>0</v>
@@ -18676,11 +18676,11 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>992223</v>
+        <v>7289583</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Diamond Toastmasters Club</t>
+          <t>Raisoni Institute's Brio Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         </is>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q186" s="9" t="n">
         <v>0</v>
@@ -18734,7 +18734,7 @@
         <v>0</v>
       </c>
       <c r="S186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T186" s="9" t="n">
         <v>0</v>
@@ -18743,13 +18743,13 @@
         <v>0</v>
       </c>
       <c r="V186" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X186" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
@@ -18773,15 +18773,15 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>28676987</v>
+        <v>992223</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Maestro Toastmasters Club</t>
+          <t>Raisoni Institute's Diamond Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -18795,13 +18795,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -18822,16 +18822,16 @@
         </is>
       </c>
       <c r="P187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R187" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T187" s="9" t="n">
         <v>0</v>
@@ -18839,14 +18839,14 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W187" s="10" t="n">
-        <v>12</v>
+      <c r="V187" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X187" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
@@ -18866,15 +18866,15 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>7073592</v>
+        <v>28676987</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Gurukul Toastmasters Club</t>
+          <t>Raisoni Maestro Toastmasters Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
@@ -18892,17 +18892,17 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J188" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K188" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="J188" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K188" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L188" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M188" s="7" t="n">
@@ -18928,10 +18928,10 @@
         <v>0</v>
       </c>
       <c r="S188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T188" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U188" s="9" t="n">
         <v>0</v>
@@ -18939,11 +18939,11 @@
       <c r="V188" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W188" s="9" t="n">
-        <v>0</v>
+      <c r="W188" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X188" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y188" s="9" t="n">
         <v>0</v>
@@ -18967,15 +18967,15 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>7735020</v>
+        <v>7073592</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Loyal Toastmasters Club</t>
+          <t>Gurukul Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L189" s="8" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         </is>
       </c>
       <c r="P189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q189" s="9" t="n">
         <v>1</v>
@@ -19033,14 +19033,14 @@
       <c r="U189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V189" s="9" t="n">
-        <v>2</v>
+      <c r="V189" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X189" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y189" s="9" t="n">
         <v>0</v>
@@ -19064,15 +19064,15 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>992337</v>
+        <v>7735020</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Emerald Toastmasters Club</t>
+          <t>Loyal Toastmasters Club</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -19086,17 +19086,17 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K190" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L190" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M190" s="7" t="n">
@@ -19113,10 +19113,10 @@
         </is>
       </c>
       <c r="P190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q190" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R190" s="9" t="n">
         <v>0</v>
@@ -19124,8 +19124,8 @@
       <c r="S190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="9" t="n">
-        <v>0</v>
+      <c r="T190" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U190" s="9" t="n">
         <v>0</v>
@@ -19137,7 +19137,7 @@
         <v>0</v>
       </c>
       <c r="X190" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y190" s="9" t="n">
         <v>0</v>
@@ -19161,11 +19161,11 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>28680923</v>
+        <v>992337</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institutes Amethyst Toastmasters Club</t>
+          <t>Raisoni Institute's Emerald Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
@@ -19183,13 +19183,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q191" s="9" t="n">
         <v>0</v>
@@ -19228,13 +19228,13 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X191" s="9" t="n">
-        <v>0</v>
+      <c r="X191" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -19258,15 +19258,15 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>6642875</v>
+        <v>28680923</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+          <t>Raisoni Institutes Amethyst Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -19280,13 +19280,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
@@ -19324,14 +19324,14 @@
       <c r="U192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V192" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W192" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="X192" s="10" t="n">
-        <v>4</v>
+      <c r="V192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X192" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y192" s="9" t="n">
         <v>0</v>
@@ -19355,93 +19355,190 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
+        <v>6642875</v>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G193" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J193" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K193" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L193" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M193" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O193" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W193" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X193" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y193" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA193" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="n">
         <v>28678983</v>
       </c>
-      <c r="D193" s="4" t="inlineStr">
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>Ultratech Rise Toastmasters Club</t>
         </is>
       </c>
-      <c r="E193" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G193" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H193" s="4" t="inlineStr">
+      <c r="E194" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G194" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="8" t="inlineStr">
+      <c r="I194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M193" s="7" t="n">
+      <c r="M194" s="7" t="n">
         <v>46387</v>
       </c>
-      <c r="N193" s="4" t="inlineStr">
+      <c r="N194" s="4" t="inlineStr">
         <is>
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O193" s="8" t="inlineStr">
+      <c r="O194" s="8" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z193" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA193" s="9" t="n">
+      <c r="P194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA193"/>
+  <autoFilter ref="A1:AA194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19528,7 +19625,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -19594,7 +19691,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -19627,7 +19724,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -19660,7 +19757,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -19693,7 +19790,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -19726,7 +19823,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -19759,7 +19856,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19825,7 +19922,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -19858,7 +19955,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -19891,7 +19988,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20155,7 +20252,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -20221,13 +20318,13 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -20254,7 +20351,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -20317,13 +20414,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>4</v>
@@ -20335,7 +20432,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -20386,13 +20483,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -20452,7 +20549,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -20485,7 +20582,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -20518,7 +20615,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -20584,7 +20681,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -20650,7 +20747,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -20683,7 +20780,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -20716,7 +20813,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -20749,7 +20846,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$197</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 69 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 69 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA196"/>
+  <dimension ref="A1:AA197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1664,14 +1664,14 @@
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>3</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -1961,8 +1961,8 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>2</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>7</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="10" t="n">
         <v>1</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-25</v>
+        <v>-6</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>5</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>84</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>56</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5650,8 +5650,8 @@
       <c r="V51" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W51" s="9" t="n">
-        <v>1</v>
+      <c r="W51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X51" s="10" t="n">
         <v>7</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>7</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>7</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>61</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9218,8 +9218,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="9" t="n">
-        <v>2</v>
+      <c r="P88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>1</v>
@@ -9240,7 +9240,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>4</v>
       </c>
       <c r="W95" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X95" s="10" t="n">
         <v>7</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10397,8 +10397,8 @@
       <c r="T100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U100" s="9" t="n">
-        <v>0</v>
+      <c r="U100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V100" s="10" t="n">
         <v>4</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10585,11 +10585,11 @@
       <c r="R102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
+      <c r="S102" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11176,11 +11176,11 @@
       <c r="U108" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W108" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         </is>
       </c>
       <c r="P126" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>1</v>
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13196,19 +13196,19 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q129" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
@@ -13390,10 +13390,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28679554</v>
+        <v>28680980</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>CGI Pune Toastmasters Club</t>
+          <t>Articulate, Resonate, Communicate (ARC) Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,17 +13751,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -13795,14 +13795,14 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W135" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X135" s="10" t="n">
-        <v>5</v>
+      <c r="V135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13811,7 +13811,7 @@
         <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28676666</v>
+        <v>28679554</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Dr D Y Patil Community Toastmaster Club</t>
+          <t>CGI Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -13886,26 +13886,26 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W136" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -13923,15 +13923,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28679580</v>
+        <v>28676666</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Teaching Titans Toastmasters Club</t>
+          <t>Dr D Y Patil Community Toastmaster Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13983,11 +13983,11 @@
       <c r="S137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V137" s="9" t="n">
         <v>0</v>
@@ -13995,8 +13995,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="9" t="n">
-        <v>0</v>
+      <c r="X137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>6097544</v>
+        <v>28679580</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters for Pune Entrepreneurs</t>
+          <t>Teaching Titans Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14069,16 +14069,16 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="10" t="n">
-        <v>2</v>
+      <c r="S138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T138" s="9" t="n">
         <v>0</v>
@@ -14087,19 +14087,19 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="10" t="n">
-        <v>7</v>
+      <c r="X138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="10" t="n">
-        <v>1</v>
+      <c r="Z138" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14113,19 +14113,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>28678211</v>
+        <v>6097544</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Burckhardt Compression Toastmasters Club 1.0</t>
+          <t>Toastmasters for Pune Entrepreneurs</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,25 +14139,25 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L139" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O139" s="7" t="inlineStr">
@@ -14166,16 +14166,16 @@
         </is>
       </c>
       <c r="P139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S139" s="9" t="n">
-        <v>0</v>
+      <c r="S139" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T139" s="9" t="n">
         <v>0</v>
@@ -14184,22 +14184,22 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="9" t="n">
-        <v>0</v>
+      <c r="X139" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>28676267</v>
+        <v>28678211</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>GCD Toastmasters Club</t>
+          <t>Burckhardt Compression Toastmasters Club 1.0</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14250,11 +14250,11 @@
         </is>
       </c>
       <c r="M140" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O140" s="7" t="inlineStr">
@@ -14280,23 +14280,23 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W140" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="X140" s="10" t="n">
-        <v>4</v>
+      <c r="V140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -14311,11 +14311,11 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>28676682</v>
+        <v>28676267</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Pattern India Toastmasters Club</t>
+          <t>GCD Toastmasters Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -14333,17 +14333,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -14381,7 +14381,7 @@
         <v>4</v>
       </c>
       <c r="W141" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>4</v>
@@ -14408,15 +14408,15 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>7448369</v>
+        <v>28676682</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters for Pune Entrepreneurs 2.0</t>
+          <t>Pattern India Toastmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
@@ -14456,8 +14456,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P142" s="10" t="n">
-        <v>4</v>
+      <c r="P142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14466,10 +14466,10 @@
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T142" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U142" s="9" t="n">
         <v>0</v>
@@ -14481,7 +14481,7 @@
         <v>4</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14501,19 +14501,19 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>6592020</v>
+        <v>7448369</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Pune Toastmasters Club</t>
+          <t>Toastmasters for Pune Entrepreneurs 2.0</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L143" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14553,8 +14553,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P143" s="9" t="n">
-        <v>0</v>
+      <c r="P143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>0</v>
@@ -14563,28 +14563,28 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W143" s="9" t="n">
-        <v>0</v>
+      <c r="V143" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W143" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>7870960</v>
+        <v>6592020</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Mastering Leadership TMC</t>
+          <t>Deutsche Bank Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,17 +14624,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L144" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M144" s="8" t="n">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14669,19 +14669,19 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z144" s="10" t="n">
-        <v>1</v>
+      <c r="Z144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA144" s="10" t="n">
         <v>1</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28677938</v>
+        <v>7870960</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Blaze Toastmasters Club</t>
+          <t>Mastering Leadership TMC</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>9</v>
+        <v>-12</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -14765,11 +14765,11 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W145" s="10" t="n">
-        <v>5</v>
+      <c r="V145" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X145" s="10" t="n">
         <v>7</v>
@@ -14796,15 +14796,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28681038</v>
+        <v>28677938</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Tata Steel Colors Toastmasters Club 2.0</t>
+          <t>Raisoni Blaze Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -14862,20 +14862,20 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" s="9" t="n">
-        <v>0</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W146" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X146" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>7757012</v>
+        <v>28681038</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of BMC Software Customer Success</t>
+          <t>Tata Steel Colors Toastmasters Club 2.0</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,17 +14915,17 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L147" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
@@ -14960,19 +14960,19 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="10" t="n">
-        <v>7</v>
+      <c r="X147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="10" t="n">
-        <v>1</v>
+      <c r="Z147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -14986,19 +14986,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>28675867</v>
+        <v>7757012</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Avalara Pune Toastmasters Club</t>
+          <t>Toastmasters Club of BMC Software Customer Success</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,10 +15012,10 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
         <v>0</v>
@@ -15026,11 +15026,11 @@
         </is>
       </c>
       <c r="M148" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O148" s="7" t="inlineStr">
@@ -15057,22 +15057,22 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>0</v>
+      <c r="X148" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA148" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>3700901</v>
+        <v>28675867</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of BMC Software</t>
+          <t>Avalara Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,25 +15109,25 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O149" s="7" t="inlineStr">
@@ -15139,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
@@ -15153,23 +15153,23 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W149" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X149" s="10" t="n">
-        <v>7</v>
+      <c r="V149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA149" s="10" t="n">
-        <v>1</v>
+      <c r="Z149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>1141787</v>
+        <v>3700901</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune</t>
+          <t>Toastmasters Club of BMC Software</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15232,29 +15232,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P150" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q150" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R150" s="10" t="n">
-        <v>3</v>
+      <c r="P150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U150" s="10" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="T150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V150" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W150" s="10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>7</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>2973814</v>
+        <v>1141787</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune - North East</t>
+          <t>Toastmasters Club of Pune</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="8" t="n">
@@ -15329,32 +15329,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R151" s="9" t="n">
-        <v>0</v>
+      <c r="P151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q151" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R151" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V151" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W151" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15378,15 +15378,15 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>28678894</v>
+        <v>2973814</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Vertiv Pune Toastmasters Club</t>
+          <t>Toastmasters Club of Pune - North East</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
         <v>1</v>
@@ -15444,20 +15444,20 @@
       <c r="U152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W152" s="9" t="n">
-        <v>0</v>
+      <c r="V152" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W152" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X152" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -15466,24 +15466,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>6539289</v>
+        <v>28678894</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Cosmic Toastmasters Club</t>
+          <t>Vertiv Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15500,10 +15500,10 @@
         <v>0</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-21</v>
+        <v>-11</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -15524,10 +15524,10 @@
         </is>
       </c>
       <c r="P153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -15535,11 +15535,11 @@
       <c r="S153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U153" s="10" t="n">
-        <v>1</v>
+      <c r="T153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
         <v>0</v>
@@ -15547,8 +15547,8 @@
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="9" t="n">
-        <v>0</v>
+      <c r="X153" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
@@ -15572,15 +15572,15 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>7709645</v>
+        <v>6539289</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>E3 Ecolab Toastmasters Club</t>
+          <t>Cosmic Toastmasters Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15597,10 +15597,10 @@
         <v>0</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-8</v>
+        <v>-21</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -15632,11 +15632,11 @@
       <c r="S154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U154" s="9" t="n">
-        <v>0</v>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V154" s="9" t="n">
         <v>0</v>
@@ -15645,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="X154" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -15669,15 +15669,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>28678780</v>
+        <v>7709645</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Michelin Toastmasters Club</t>
+          <t>E3 Ecolab Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
@@ -15717,38 +15717,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P155" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q155" s="10" t="n">
+      <c r="P155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R155" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T155" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U155" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V155" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W155" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X155" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="10" t="n">
-        <v>1</v>
+      <c r="Z155" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -15766,15 +15766,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>28681041</v>
+        <v>28678780</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Rehlko Toastmasters Club</t>
+          <t>Michelin Toastmasters Club</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15788,17 +15788,17 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L156" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M156" s="8" t="n">
@@ -15814,38 +15814,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q156" s="9" t="n">
-        <v>0</v>
+      <c r="P156" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q156" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V156" s="9" t="n">
-        <v>0</v>
+      <c r="S156" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X156" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -15863,15 +15863,15 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>7780150</v>
+        <v>28681041</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Wonders of Women Toastmasters Club</t>
+          <t>Rehlko Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,17 +15885,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L157" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -15915,34 +15915,34 @@
         <v>0</v>
       </c>
       <c r="Q157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T157" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X157" s="10" t="n">
-        <v>5</v>
+      <c r="X157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="10" t="n">
-        <v>1</v>
+      <c r="Z157" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -15956,19 +15956,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>5144305</v>
+        <v>7780150</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Barclays Pune Toastmasters Club</t>
+          <t>Wonders of Women Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -15982,13 +15982,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16009,25 +16009,25 @@
         </is>
       </c>
       <c r="P158" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R158" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S158" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16057,15 +16057,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>28679346</v>
+        <v>5144305</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Club 3.0</t>
+          <t>Barclays Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-20</v>
+        <v>-14</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -16130,13 +16130,13 @@
         <v>0</v>
       </c>
       <c r="X159" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -16154,15 +16154,15 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>7922639</v>
+        <v>28679346</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters 3.0</t>
+          <t>Eaton Toastmasters Club 3.0</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-9</v>
+        <v>-20</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q160" s="9" t="n">
         <v>0</v>
@@ -16214,26 +16214,26 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U160" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V160" s="10" t="n">
+      <c r="T160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W160" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X160" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="10" t="n">
-        <v>1</v>
+      <c r="Z160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16251,15 +16251,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>28679461</v>
+        <v>7922639</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Serum Pune Toastmasters Club</t>
+          <t>John Deere Pune Toastmasters 3.0</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q161" s="9" t="n">
         <v>0</v>
@@ -16311,26 +16311,26 @@
       <c r="S161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U161" s="9" t="n">
-        <v>0</v>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V161" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W161" s="10" t="n">
-        <v>15</v>
+      <c r="W161" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X161" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -16344,19 +16344,19 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>1813871</v>
+        <v>28679461</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>ADP Pune Toastmasters</t>
+          <t>Serum Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16373,10 +16373,10 @@
         <v>0</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -16399,14 +16399,14 @@
       <c r="P162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" s="10" t="n">
-        <v>2</v>
+      <c r="Q162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S162" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T162" s="9" t="n">
         <v>0</v>
@@ -16414,11 +16414,11 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" s="9" t="n">
-        <v>0</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W162" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="X162" s="10" t="n">
         <v>7</v>
@@ -16445,15 +16445,15 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>6006628</v>
+        <v>1813871</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Allstate Toastmasters Club Pune</t>
+          <t>ADP Pune Toastmasters</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16467,17 +16467,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L163" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -16494,16 +16494,16 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q163" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R163" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S163" s="10" t="n">
-        <v>2</v>
+      <c r="R163" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="T163" s="9" t="n">
         <v>0</v>
@@ -16511,11 +16511,11 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>2</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>7</v>
@@ -16523,8 +16523,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="10" t="n">
-        <v>1</v>
+      <c r="Z163" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -16542,15 +16542,15 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>28677687</v>
+        <v>6006628</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Excellence Club</t>
+          <t>Allstate Toastmasters Club Pune</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16564,13 +16564,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -16591,16 +16591,16 @@
         </is>
       </c>
       <c r="P164" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q164" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" s="9" t="n">
-        <v>0</v>
+      <c r="R164" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T164" s="9" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -16620,8 +16620,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -16639,15 +16639,15 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>6691907</v>
+        <v>28677687</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>RISE Toastmasters Club, Magarpatta</t>
+          <t>Eaton Toastmasters Excellence Club</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -16661,17 +16661,17 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L165" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M165" s="8" t="n">
@@ -16688,7 +16688,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q165" s="9" t="n">
         <v>0</v>
@@ -16697,10 +16697,10 @@
         <v>0</v>
       </c>
       <c r="S165" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T165" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T165" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U165" s="9" t="n">
         <v>0</v>
@@ -16708,8 +16708,8 @@
       <c r="V165" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W165" s="10" t="n">
-        <v>12</v>
+      <c r="W165" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>7</v>
@@ -16717,8 +16717,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="10" t="n">
-        <v>1</v>
+      <c r="Z165" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -16732,19 +16732,19 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>28678887</v>
+        <v>6691907</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Allianz Technology Toastmasters Club 2.0</t>
+          <t>RISE Toastmasters Club, Magarpatta</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -16758,25 +16758,25 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="L166" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-13</v>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O166" s="7" t="inlineStr">
@@ -16784,8 +16784,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P166" s="9" t="n">
-        <v>1</v>
+      <c r="P166" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q166" s="9" t="n">
         <v>0</v>
@@ -16794,31 +16794,31 @@
         <v>0</v>
       </c>
       <c r="S166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" s="9" t="n">
-        <v>0</v>
+      <c r="V166" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W166" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X166" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -16833,15 +16833,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>28680266</v>
+        <v>28678887</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Hoerbiger Pune Toastmasters Club</t>
+          <t>Allianz Technology Toastmasters Club 2.0</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -16855,25 +16855,25 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O167" s="7" t="inlineStr">
@@ -16882,7 +16882,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -16906,16 +16906,16 @@
         <v>0</v>
       </c>
       <c r="X167" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA167" s="10" t="n">
-        <v>1</v>
+      <c r="Z167" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA167" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -16930,15 +16930,15 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>2187981</v>
+        <v>28680266</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters Club</t>
+          <t>Hoerbiger Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -16952,17 +16952,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L168" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -16997,19 +16997,19 @@
         <v>0</v>
       </c>
       <c r="V168" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X168" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -17027,15 +17027,15 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>7327561</v>
+        <v>2187981</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Teradata Pune Toastmasters Club</t>
+          <t>John Deere Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17094,19 +17094,19 @@
         <v>0</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X169" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="10" t="n">
-        <v>1</v>
+      <c r="Z169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
@@ -17124,15 +17124,15 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1543586</v>
+        <v>7327561</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Pune South East</t>
+          <t>Teradata Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17146,17 +17146,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -17173,10 +17173,10 @@
         </is>
       </c>
       <c r="P170" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q170" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" s="9" t="n">
         <v>0</v>
@@ -17184,20 +17184,20 @@
       <c r="S170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T170" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U170" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V170" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W170" s="10" t="n">
-        <v>5</v>
+      <c r="T170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W170" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X170" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -17217,19 +17217,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>6783469</v>
+        <v>1543586</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>BNY Prestige Pune Toastmasters Club</t>
+          <t>Toastmasters Club of Pune South East</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -17243,17 +17243,17 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L171" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R171" s="9" t="n">
         <v>0</v>
@@ -17281,26 +17281,26 @@
       <c r="S171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V171" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W171" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" s="9" t="n">
-        <v>3</v>
+      <c r="T171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V171" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W171" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X171" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z171" s="9" t="n">
-        <v>0</v>
+      <c r="Z171" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA171" s="10" t="n">
         <v>1</v>
@@ -17318,11 +17318,11 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>28676238</v>
+        <v>6783469</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Danfoss Toastmasters Club, Pune</t>
+          <t>BNY Prestige Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
@@ -17340,13 +17340,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -17384,20 +17384,20 @@
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="9" t="n">
+      <c r="V172" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W172" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W172" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X172" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="10" t="n">
-        <v>1</v>
+      <c r="Z172" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -17415,15 +17415,15 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>28680588</v>
+        <v>28676238</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Eaton TMC 2.0</t>
+          <t>Danfoss Toastmasters Club, Pune</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -17440,14 +17440,14 @@
         <v>15</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L173" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M173" s="8" t="n">
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q173" s="9" t="n">
         <v>0</v>
@@ -17481,20 +17481,20 @@
       <c r="U173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V173" s="9" t="n">
-        <v>1</v>
+      <c r="V173" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X173" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="9" t="n">
-        <v>0</v>
+      <c r="Z173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
@@ -17512,15 +17512,15 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1114159</v>
+        <v>28680588</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Eaton Toastmasters Club</t>
+          <t>Eaton TMC 2.0</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17534,17 +17534,17 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L174" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>15</v>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M174" s="8" t="n">
@@ -17563,8 +17563,8 @@
       <c r="P174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" s="10" t="n">
-        <v>2</v>
+      <c r="Q174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R174" s="9" t="n">
         <v>0</v>
@@ -17585,13 +17585,13 @@
         <v>0</v>
       </c>
       <c r="X174" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="10" t="n">
-        <v>1</v>
+      <c r="Z174" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -17609,15 +17609,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>7850568</v>
+        <v>1114159</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>John Deere Pune Toastmasters 2.0</t>
+          <t>Eaton Toastmasters Club</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17631,13 +17631,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -17660,26 +17660,26 @@
       <c r="P175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" s="9" t="n">
-        <v>1</v>
+      <c r="Q175" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T175" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U175" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V175" s="10" t="n">
-        <v>4</v>
+      <c r="S175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W175" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X175" s="10" t="n">
         <v>5</v>
@@ -17697,24 +17697,24 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>5297378</v>
+        <v>7850568</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Barclays Pune 2 Toastmasters</t>
+          <t>John Deere Pune Toastmasters 2.0</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -17728,10 +17728,10 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K176" s="4" t="n">
         <v>-12</v>
@@ -17755,31 +17755,31 @@
         </is>
       </c>
       <c r="P176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" s="10" t="n">
+      <c r="T176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V176" s="9" t="n">
-        <v>0</v>
+      <c r="V176" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W176" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X176" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -17803,15 +17803,15 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>28676691</v>
+        <v>5297378</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>BNY Mic Master's Club</t>
+          <t>Barclays Pune 2 Toastmasters</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -17852,16 +17852,16 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q177" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R177" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T177" s="9" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="X177" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -17900,15 +17900,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>28677096</v>
+        <v>28676691</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>EEEC Pune Toastmasters Club</t>
+          <t>BNY Mic Master's Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -17948,11 +17948,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P178" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q178" s="10" t="n">
-        <v>2</v>
+      <c r="P178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R178" s="9" t="n">
         <v>0</v>
@@ -17966,14 +17966,14 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="10" t="n">
+      <c r="V178" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W178" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X178" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W178" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X178" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y178" s="9" t="n">
         <v>0</v>
@@ -17997,15 +17997,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>7289566</v>
+        <v>28677096</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Expedition Toastmasters Pune</t>
+          <t>EEEC Pune Toastmasters Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,17 +18019,17 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J179" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L179" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L179" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
@@ -18045,17 +18045,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q179" s="9" t="n">
-        <v>0</v>
+      <c r="P179" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q179" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S179" s="10" t="n">
-        <v>2</v>
+      <c r="S179" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T179" s="9" t="n">
         <v>0</v>
@@ -18067,7 +18067,7 @@
         <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -18094,11 +18094,11 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>7300474</v>
+        <v>7289566</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Kharadi Toastmasters Club</t>
+          <t>Expedition Toastmasters Pune</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
@@ -18116,17 +18116,17 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L180" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
@@ -18146,13 +18146,13 @@
         <v>0</v>
       </c>
       <c r="Q180" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S180" s="9" t="n">
-        <v>0</v>
+      <c r="S180" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T180" s="9" t="n">
         <v>0</v>
@@ -18163,11 +18163,11 @@
       <c r="V180" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W180" s="10" t="n">
-        <v>4</v>
+      <c r="W180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X180" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -18187,19 +18187,19 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>6716037</v>
+        <v>7300474</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Aurangabad Toastmasters</t>
+          <t>Kharadi Toastmasters Club</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -18213,10 +18213,10 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K181" s="4" t="n">
         <v>-3</v>
@@ -18243,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="Q181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
@@ -18257,11 +18257,11 @@
       <c r="U181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W181" s="9" t="n">
-        <v>0</v>
+      <c r="V181" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W181" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>6</v>
@@ -18288,11 +18288,11 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>28680879</v>
+        <v>6716037</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Everseen Toastmasters Club</t>
+          <t>Aurangabad Toastmasters</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -18310,17 +18310,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M182" s="8" t="n">
@@ -18355,7 +18355,7 @@
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -18367,7 +18367,7 @@
         <v>0</v>
       </c>
       <c r="Z182" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA182" s="10" t="n">
         <v>1</v>
@@ -18385,11 +18385,11 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>6941712</v>
+        <v>28680879</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club of Nashik</t>
+          <t>Everseen Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
@@ -18407,17 +18407,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L183" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -18451,20 +18451,20 @@
       <c r="U183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V183" s="10" t="n">
-        <v>4</v>
+      <c r="V183" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X183" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="X183" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z183" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="AA183" s="10" t="n">
         <v>1</v>
@@ -18482,11 +18482,11 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>28677802</v>
+        <v>6941712</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Voice of E76</t>
+          <t>Toastmasters Club of Nashik</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
@@ -18504,13 +18504,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X184" s="10" t="n">
         <v>4</v>
@@ -18579,11 +18579,11 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>28675765</v>
+        <v>28677802</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Wagholi Toastmasters Club</t>
+          <t>Voice of E76</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
@@ -18601,13 +18601,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>0</v>
       </c>
       <c r="S185" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T185" s="9" t="n">
         <v>0</v>
@@ -18645,20 +18645,20 @@
       <c r="U185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V185" s="9" t="n">
-        <v>0</v>
+      <c r="V185" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X185" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="10" t="n">
-        <v>1</v>
+      <c r="Z185" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -18672,19 +18672,19 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>5757009</v>
+        <v>28675765</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>IIM Nagpur Toastmasters Club</t>
+          <t>Wagholi Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>0</v>
       </c>
       <c r="S186" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T186" s="9" t="n">
         <v>0</v>
@@ -18748,14 +18748,14 @@
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="9" t="n">
-        <v>0</v>
+      <c r="X186" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="9" t="n">
-        <v>0</v>
+      <c r="Z186" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA186" s="10" t="n">
         <v>1</v>
@@ -18773,15 +18773,15 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>3531688</v>
+        <v>5757009</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Nagpur Toastmasters Club</t>
+          <t>IIM Nagpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -18795,17 +18795,17 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L187" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M187" s="8" t="n">
@@ -18822,7 +18822,7 @@
         </is>
       </c>
       <c r="P187" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q187" s="9" t="n">
         <v>0</v>
@@ -18831,28 +18831,28 @@
         <v>0</v>
       </c>
       <c r="S187" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T187" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="10" t="n">
-        <v>4</v>
+      <c r="V187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W187" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X187" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="X187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="10" t="n">
-        <v>1</v>
+      <c r="Z187" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
@@ -18870,15 +18870,15 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>7289583</v>
+        <v>3531688</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Brio Toastmasters Club</t>
+          <t>Nagpur Toastmasters Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -18892,13 +18892,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
@@ -18919,31 +18919,31 @@
         </is>
       </c>
       <c r="P188" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q188" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U188" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W188" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S188" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V188" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W188" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X188" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y188" s="9" t="n">
         <v>0</v>
@@ -18967,11 +18967,11 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>992223</v>
+        <v>7289583</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Diamond Toastmasters Club</t>
+          <t>Raisoni Institute's Brio Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         </is>
       </c>
       <c r="P189" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q189" s="9" t="n">
         <v>0</v>
@@ -19025,7 +19025,7 @@
         <v>0</v>
       </c>
       <c r="S189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T189" s="9" t="n">
         <v>0</v>
@@ -19034,13 +19034,13 @@
         <v>0</v>
       </c>
       <c r="V189" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W189" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X189" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y189" s="9" t="n">
         <v>0</v>
@@ -19064,15 +19064,15 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>28676987</v>
+        <v>992223</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Maestro Toastmasters Club</t>
+          <t>Raisoni Institute's Diamond Toastmasters Club</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>10</v>
@@ -19086,13 +19086,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
@@ -19113,16 +19113,16 @@
         </is>
       </c>
       <c r="P190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S190" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T190" s="9" t="n">
         <v>0</v>
@@ -19130,14 +19130,14 @@
       <c r="U190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V190" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W190" s="10" t="n">
-        <v>12</v>
+      <c r="V190" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W190" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X190" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y190" s="9" t="n">
         <v>0</v>
@@ -19157,19 +19157,19 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>7073592</v>
+        <v>28676987</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Gurukul Toastmasters Club</t>
+          <t>Raisoni Maestro Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -19183,17 +19183,17 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J191" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K191" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K191" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L191" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
@@ -19219,22 +19219,22 @@
         <v>0</v>
       </c>
       <c r="S191" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T191" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U191" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T191" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V191" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W191" s="9" t="n">
-        <v>0</v>
+      <c r="W191" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="X191" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -19258,15 +19258,15 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>7735020</v>
+        <v>7073592</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Loyal Toastmasters Club</t>
+          <t>Gurukul Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>10</v>
@@ -19283,10 +19283,10 @@
         <v>11</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="P192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q192" s="9" t="n">
         <v>1</v>
@@ -19321,8 +19321,8 @@
       <c r="T192" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U192" s="9" t="n">
-        <v>0</v>
+      <c r="U192" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V192" s="10" t="n">
         <v>4</v>
@@ -19331,7 +19331,7 @@
         <v>0</v>
       </c>
       <c r="X192" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y192" s="9" t="n">
         <v>0</v>
@@ -19355,15 +19355,15 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>992337</v>
+        <v>7735020</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institute's Emerald Toastmasters Club</t>
+          <t>Loyal Toastmasters Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>10</v>
@@ -19377,13 +19377,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -19404,10 +19404,10 @@
         </is>
       </c>
       <c r="P193" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R193" s="9" t="n">
         <v>0</v>
@@ -19415,20 +19415,20 @@
       <c r="S193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T193" s="9" t="n">
-        <v>0</v>
+      <c r="T193" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V193" s="9" t="n">
-        <v>2</v>
+      <c r="V193" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W193" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X193" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y193" s="9" t="n">
         <v>0</v>
@@ -19452,11 +19452,11 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>28680923</v>
+        <v>992337</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Raisoni Institutes Amethyst Toastmasters Club</t>
+          <t>Raisoni Institute's Emerald Toastmasters Club</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
@@ -19474,17 +19474,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="8" t="n">
@@ -19501,7 +19501,7 @@
         </is>
       </c>
       <c r="P194" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q194" s="9" t="n">
         <v>0</v>
@@ -19519,13 +19519,13 @@
         <v>0</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X194" s="9" t="n">
-        <v>0</v>
+      <c r="X194" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y194" s="9" t="n">
         <v>0</v>
@@ -19549,15 +19549,15 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>6642875</v>
+        <v>28680923</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+          <t>Raisoni Institutes Amethyst Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -19571,13 +19571,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
@@ -19615,14 +19615,14 @@
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W195" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="X195" s="10" t="n">
-        <v>4</v>
+      <c r="V195" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W195" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y195" s="9" t="n">
         <v>0</v>
@@ -19646,93 +19646,190 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
+        <v>6642875</v>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>RAISONI INSTITUTES'S CATALYST TOASTMASTER CLUB</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F196" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G196" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J196" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K196" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="L196" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M196" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O196" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W196" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="X196" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA196" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="n">
         <v>28678983</v>
       </c>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="D197" s="4" t="inlineStr">
         <is>
           <t>Ultratech Rise Toastmasters Club</t>
         </is>
       </c>
-      <c r="E196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G196" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
+      <c r="E197" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G197" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
         <is>
           <t>Smedley</t>
         </is>
       </c>
-      <c r="I196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="7" t="inlineStr">
+      <c r="I197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M196" s="8" t="n">
+      <c r="M197" s="8" t="n">
         <v>46387</v>
       </c>
-      <c r="N196" s="4" t="inlineStr">
+      <c r="N197" s="4" t="inlineStr">
         <is>
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O196" s="7" t="inlineStr">
+      <c r="O197" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
-      <c r="P196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z196" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA196" s="9" t="n">
+      <c r="P197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA196"/>
+  <autoFilter ref="A1:AA197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19852,7 +19949,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -19885,7 +19982,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -20116,7 +20213,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -20347,13 +20444,13 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -20446,7 +20543,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -20479,13 +20576,13 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -20512,7 +20609,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -20527,7 +20624,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -20644,13 +20741,13 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -20707,16 +20804,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -20725,7 +20822,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -20908,13 +21005,13 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -20923,7 +21020,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -20974,7 +21071,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>

--- a/docs/d/226/inyear.xlsx
+++ b/docs/d/226/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 17 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 69 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 69 clubs short</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1667,8 +1667,8 @@
       <c r="T10" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" s="9" t="n">
-        <v>0</v>
+      <c r="U10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V10" s="10" t="n">
         <v>4</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="10" t="n">
         <v>7</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>1</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>4</v>
       </c>
       <c r="W18" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2528,8 +2528,8 @@
       <c r="P19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" s="9" t="n">
-        <v>1</v>
+      <c r="Q19" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R19" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X32" s="10" t="n">
         <v>7</v>
@@ -4392,8 +4392,8 @@
       <c r="W38" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="X38" s="9" t="n">
-        <v>0</v>
+      <c r="X38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4486,8 +4486,8 @@
       <c r="V39" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>3</v>
+      <c r="W39" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="10" t="n">
         <v>7</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>5</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>84</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5253,8 +5253,8 @@
       <c r="S47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
+      <c r="T47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U47" s="9" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6599,11 +6599,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P61" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q61" s="9" t="n">
-        <v>1</v>
+      <c r="P61" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q61" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7382,7 +7382,7 @@
         <v>2</v>
       </c>
       <c r="R69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9221,8 +9221,8 @@
       <c r="P88" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9715,8 +9715,8 @@
       <c r="S93" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="P95" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q95" s="9" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10497,8 +10497,8 @@
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="9" t="n">
-        <v>3</v>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11367,8 +11367,8 @@
       <c r="T110" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U110" s="9" t="n">
-        <v>0</v>
+      <c r="U110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V110" s="10" t="n">
         <v>4</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>4</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13195,8 +13195,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P129" s="9" t="n">
-        <v>3</v>
+      <c r="P129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q129" s="10" t="n">
         <v>2</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>4</v>
       </c>
       <c r="W131" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -14557,7 +14557,7 @@
         <v>4</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -16079,13 +16079,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -16220,11 +16220,11 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" s="9" t="n">
-        <v>0</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W160" s="10" t="n">
+        <v>20</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>4</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16505,8 +16505,8 @@
       <c r="S163" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T163" s="9" t="n">
-        <v>0</v>
+      <c r="T163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="9" t="n">
         <v>0</v>
@@ -16788,7 +16788,7 @@
         <v>4</v>
       </c>
       <c r="Q166" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R166" s="9" t="n">
         <v>0</v>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -17285,13 +17285,13 @@
         <v>1</v>
       </c>
       <c r="U171" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V171" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W171" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>6</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>4</v>
       </c>
       <c r="W173" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X173" s="10" t="n">
         <v>5</v>
@@ -17728,13 +17728,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -17825,13 +17825,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -17869,11 +17869,11 @@
       <c r="U177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="9" t="n">
-        <v>0</v>
+      <c r="V177" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X177" s="10" t="n">
         <v>7</v>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Aurangabad Toastmasters</t>
+          <t>CSN Toastmasters</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -19221,8 +19221,8 @@
       <c r="S191" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T191" s="9" t="n">
-        <v>0</v>
+      <c r="T191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U191" s="9" t="n">
         <v>0</v>
@@ -19949,7 +19949,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20015,7 +20015,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -20147,13 +20147,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -20180,7 +20180,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -20279,13 +20279,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -20444,7 +20444,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -20492,7 +20492,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -20510,7 +20510,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -20576,7 +20576,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -20642,7 +20642,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -20741,7 +20741,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -20972,7 +20972,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -20987,7 +20987,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -21005,7 +21005,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -21104,7 +21104,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -21170,7 +21170,7 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
